--- a/output/pdf_financials_xlsx/SPIR.xlsx
+++ b/output/pdf_financials_xlsx/SPIR.xlsx
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.375491</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.929194</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.050391</v>
       </c>
     </row>
     <row r="35">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.375491</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.929194</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.050391</v>
       </c>
     </row>
     <row r="37">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.006447</v>
+        <v>0.630956</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.975664</v>
+        <v>0.04647</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.027411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">

--- a/output/pdf_financials_xlsx/SPIR.xlsx
+++ b/output/pdf_financials_xlsx/SPIR.xlsx
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1.966564</v>
+        <v>-1.967315</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-11.19255</v>
+        <v>-22.3851</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-4.482563</v>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.000751</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>11.19255</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.966564</v>
+        <v>-1.967315</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-11.19255</v>
+        <v>-22.3851</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.482563</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.966564</v>
+        <v>-1.967315</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-11.19255</v>
+        <v>-22.3851</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.482563</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.03817385624569528</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.7000459999999999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>2.202144</v>
       </c>
     </row>
     <row r="65">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.058249</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.388692</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.169761</v>
       </c>
     </row>
     <row r="68">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.007373</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.192643</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.011077</v>
       </c>
     </row>
     <row r="111">
@@ -3825,7 +3825,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.007373</v>
       </c>
@@ -4574,7 +4578,11 @@
           <t>Proceeds from issuance of units in private placement</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>0.068615</v>
       </c>
@@ -8181,7 +8189,11 @@
           <t>Loss before income tax recovery</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>-1.965813</v>
       </c>
@@ -8210,7 +8222,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E181" s="5" t="n">
         <v>-0.000751</v>
       </c>
